--- a/data/import/fabric/fabric.xlsx
+++ b/data/import/fabric/fabric.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,16 +486,376 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bmw-check</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BMW Check</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bmw-m-pattern</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>fabric</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BMW M Pattern</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>houndstooth-plaid</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Houndstooth Plaid</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mercedes-check</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mercedes Check </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mercedes-rodeo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mercedes Rodeo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mercedes-tartan</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mercedes Tartan</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Porsche Check</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>porsche-herringbone</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Porsche Herringbone</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>porsche-madras</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Porsche Madras</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Porsche Pepita</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Porsche Pinstripe</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>porsche-plaid</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Porsche Plaid</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>porsche-script</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Porsche Script</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porsche Studio </t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Porsche Tartan</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>selected-plaid</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Selected Plaid</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spirit of Le Mans</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
         </is>
       </c>
     </row>
@@ -648,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,16 +1094,1482 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fa1836</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bmw-check</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FA1836</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fa5990</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>fabric</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bmw-m-pattern</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FA5990</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fa8765</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>houndstooth-plaid</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FA8765</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fa8475</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mercedes-check</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FA8475</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fa8598</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mercedes-rodeo</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FA8598</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fa8626</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mercedes-tartan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FA8626</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>fa8637</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mercedes-tartan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FA8637</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8637.jpg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8637.jpg</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8637.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>fa8045</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FA8045</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>fa8057</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FA8057</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8057.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8057.jpg</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8057.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fa8063</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FA8063</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8063.jpg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8063.jpg</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8063.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fa3570</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>porsche-herringbone</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FA3570</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fa8326</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>porsche-madras</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FA8326</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fa8354</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>porsche-madras</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FA8354</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8354.jpg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8354.jpg</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8354.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fa8013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FA8013</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fa8026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FA8026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8026.jpg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8026.jpg</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fa8065</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FA8065</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8065.jpg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8065.jpg</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8065.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fa8074</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FA8074</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8074.jpg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8074.jpg</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8074.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fa8093</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FA8093</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8093.jpg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8093.jpg</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8093.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>fa8094</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FA8094</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8094.jpg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8094.jpg</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8094.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fa3018</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FA3018</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fa3055</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FA3055</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3055.jpg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3055.jpg</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3055.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>fa3067</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FA3067</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3067.jpg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3067.jpg</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3067.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>fa3074</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FA3074</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3074.jpg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3074.jpg</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3074.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fa8525</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>porsche-plaid</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FA8525</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fa3132</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>porsche-script</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FA3132</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fa3217</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>porsche-script</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FA3217</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fa3258</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>porsche-script</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FA3258</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fa3272</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>porsche-script</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FA3272</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fa8118</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FA8118</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fa8128</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FA8128</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8128.jpg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8128.jpg</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8128.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>fa8165</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FA8165</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8165.jpg</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8165.jpg</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8165.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fa8166</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FA8166</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fa8217</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FA8217</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fa8237</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FA8237</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8237 Black Watch.jpg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8237 Black Watch.jpg</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8237 Black Watch.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fa8271</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>FA8271</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8271 Mackenzie.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8271 Mackenzie.jpg</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8271 Mackenzie.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fa8517</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>selected-plaid</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FA8517</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fa8553</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>selected-plaid</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>FA8553</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fa2002</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>FA2002</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fa2202</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FA2202</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fa2729</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>FA2729</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
         </is>
       </c>
     </row>
@@ -860,7 +2686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,6 +2716,606 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fa1836</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fa5990</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fa8765</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fa8475</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fa8598</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fa8626</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>fa8637</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Tartan/FA8637.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>fa8045</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>fa8057</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8057.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fa8063</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Check/FA8063.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fa3570</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fa8326</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fa8354</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Madras/FA8354.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fa8013</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fa8026</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8026.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fa8065</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8065.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fa8074</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8074.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fa8093</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8093.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>fa8094</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pepita/FA8094.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>fa3018</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>fa3055</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3055.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>fa3067</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3067.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>fa3074</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3074.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fa8525</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fa3132</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fa3217</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fa3258</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fa3272</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fa8118</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fa8128</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8128.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>fa8165</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8165.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fa8166</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fa8217</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fa8237</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8237 Black Watch.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fa8271</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Porsche Tartan/FA8271 Mackenzie.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fa8517</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fa8553</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fa2002</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fa2202</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fa2729</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/import/fabric/fabric.xlsx
+++ b/data/import/fabric/fabric.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
+          <t>/uploads/fabric/Cover/FA1836.jpg</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
+          <t>/uploads/fabric/Cover/FA5990.jpg</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
+          <t>/uploads/fabric/Cover/FA8765.jpg</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
+          <t>/uploads/fabric/Cover/FA8475.jpg</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
+          <t>/uploads/fabric/Cover/FA8598.jpg</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
+          <t>/uploads/fabric/Cover/FA8626.jpg</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
+          <t>/uploads/fabric/Cover/FA8045.jpg</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
+          <t>/uploads/fabric/Cover/FA3570.jpg</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
+          <t>/uploads/fabric/Cover/FA8326.jpg</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
+          <t>/uploads/fabric/Cover/FA8013.jpg</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
+          <t>/uploads/fabric/Cover/FA3018.jpg</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
+          <t>/uploads/fabric/Cover/FA8525.jpg</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+          <t>/uploads/fabric/Cover/FA3132.jpg</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
+          <t>/uploads/fabric/Cover/FA8118.jpg</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
+          <t>/uploads/fabric/Cover/FA8217.jpg</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
+          <t>/uploads/fabric/Cover/FA8517.jpg</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+          <t>/uploads/fabric/Cover/FA2002.jpg</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1059,35 +1059,40 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>preview_image</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>summary_en</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>summary_ja</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>seo_title_en</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>seo_title_ja</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>seo_description_en</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>seo_description_ja</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>seo_image</t>
         </is>
@@ -1124,7 +1129,12 @@
           <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA1836.jpg</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
         </is>
@@ -1161,7 +1171,12 @@
           <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA5990.jpg</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
         </is>
@@ -1198,7 +1213,12 @@
           <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8765.jpg</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
         </is>
@@ -1235,7 +1255,12 @@
           <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8475.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
         </is>
@@ -1272,7 +1297,12 @@
           <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8598.jpg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
         </is>
@@ -1309,7 +1339,12 @@
           <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8626.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
         </is>
@@ -1346,7 +1381,12 @@
           <t>/uploads/fabric/Mercedes Tartan/FA8637.jpg</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8637.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>/uploads/fabric/Mercedes Tartan/FA8637.jpg</t>
         </is>
@@ -1383,7 +1423,12 @@
           <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8045.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
         </is>
@@ -1420,7 +1465,12 @@
           <t>/uploads/fabric/Porsche Check/FA8057.jpg</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8057.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Check/FA8057.jpg</t>
         </is>
@@ -1457,7 +1507,12 @@
           <t>/uploads/fabric/Porsche Check/FA8063.jpg</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8063.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Check/FA8063.jpg</t>
         </is>
@@ -1494,7 +1549,12 @@
           <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3570.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
         </is>
@@ -1531,7 +1591,12 @@
           <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8326.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
         </is>
@@ -1568,7 +1633,12 @@
           <t>/uploads/fabric/Porsche Madras/FA8354.jpg</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8354.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Madras/FA8354.jpg</t>
         </is>
@@ -1605,7 +1675,12 @@
           <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8013.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
         </is>
@@ -1642,7 +1717,12 @@
           <t>/uploads/fabric/Porsche Pepita/FA8026.jpg</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8026.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8026.jpg</t>
         </is>
@@ -1679,7 +1759,12 @@
           <t>/uploads/fabric/Porsche Pepita/FA8065.jpg</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8065.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8065.jpg</t>
         </is>
@@ -1716,7 +1801,12 @@
           <t>/uploads/fabric/Porsche Pepita/FA8074.jpg</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8074.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8074.jpg</t>
         </is>
@@ -1753,7 +1843,12 @@
           <t>/uploads/fabric/Porsche Pepita/FA8093.jpg</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8093.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8093.jpg</t>
         </is>
@@ -1790,7 +1885,12 @@
           <t>/uploads/fabric/Porsche Pepita/FA8094.jpg</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8094.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8094.jpg</t>
         </is>
@@ -1827,7 +1927,12 @@
           <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3018.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
         </is>
@@ -1864,7 +1969,12 @@
           <t>/uploads/fabric/Porsche Pinstripe/FA3055.jpg</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3055.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pinstripe/FA3055.jpg</t>
         </is>
@@ -1901,7 +2011,12 @@
           <t>/uploads/fabric/Porsche Pinstripe/FA3067.jpg</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3067.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pinstripe/FA3067.jpg</t>
         </is>
@@ -1938,7 +2053,12 @@
           <t>/uploads/fabric/Porsche Pinstripe/FA3074.jpg</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3074.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pinstripe/FA3074.jpg</t>
         </is>
@@ -1975,7 +2095,12 @@
           <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8525.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
         </is>
@@ -2012,7 +2137,12 @@
           <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3132.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
         </is>
@@ -2049,7 +2179,12 @@
           <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3217.jpg</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
         </is>
@@ -2086,7 +2221,12 @@
           <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3258.jpg</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
         </is>
@@ -2123,7 +2263,12 @@
           <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA3272.jpg</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
         </is>
@@ -2160,7 +2305,12 @@
           <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8118.jpg</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
         </is>
@@ -2197,7 +2347,12 @@
           <t>/uploads/fabric/Porsche Studio /FA8128.jpg</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8128.jpg</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8128.jpg</t>
         </is>
@@ -2234,7 +2389,12 @@
           <t>/uploads/fabric/Porsche Studio /FA8165.jpg</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8165.jpg</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8165.jpg</t>
         </is>
@@ -2271,7 +2431,8 @@
           <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="J33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
         </is>
@@ -2308,7 +2469,12 @@
           <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8217.jpg</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
         </is>
@@ -2345,7 +2511,12 @@
           <t>/uploads/fabric/Porsche Tartan/FA8237 Black Watch.jpg</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8237.jpg</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Tartan/FA8237 Black Watch.jpg</t>
         </is>
@@ -2382,7 +2553,12 @@
           <t>/uploads/fabric/Porsche Tartan/FA8271 Mackenzie.jpg</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8271.jpg</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Tartan/FA8271 Mackenzie.jpg</t>
         </is>
@@ -2419,7 +2595,12 @@
           <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8517.jpg</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
         </is>
@@ -2456,7 +2637,12 @@
           <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8553.jpg</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
         </is>
@@ -2493,7 +2679,12 @@
           <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA2002.jpg</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
         </is>
@@ -2530,7 +2721,12 @@
           <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA2202.jpg</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
         </is>
@@ -2567,7 +2763,12 @@
           <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA2729.jpg</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
         </is>

--- a/data/import/fabric/fabric.xlsx
+++ b/data/import/fabric/fabric.xlsx
@@ -2431,7 +2431,11 @@
           <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8166.jpg</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>

--- a/data/import/fabric/fabric.xlsx
+++ b/data/import/fabric/fabric.xlsx
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
+          <t>/uploads/fabric/Case/FA1836.jpg</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
+          <t>/uploads/fabric/Case/FA5990.jpg</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
+          <t>/uploads/fabric/Case/FA8765.jpg</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
+          <t>/uploads/fabric/Case/FA8475.jpg</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
+          <t>/uploads/fabric/Case/FA8598.jpg</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
+          <t>/uploads/fabric/Case/FA8626.jpg</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Mercedes Tartan/FA8637.jpg</t>
+          <t>/uploads/fabric/Case/FA8637.jpg</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
+          <t>/uploads/fabric/Case/FA8045.jpg</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Check/FA8057.jpg</t>
+          <t>/uploads/fabric/Case/FA8057.jpg</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Check/FA8063.jpg</t>
+          <t>/uploads/fabric/Case/FA8063.jpg</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
+          <t>/uploads/fabric/Case/FA3570.jpg</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
+          <t>/uploads/fabric/Case/FA8326.jpg</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Madras/FA8354.jpg</t>
+          <t>/uploads/fabric/Case/FA8354.jpg</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
+          <t>/uploads/fabric/Case/FA8013.jpg</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pepita/FA8026.jpg</t>
+          <t>/uploads/fabric/Case/FA8026.jpg</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pepita/FA8065.jpg</t>
+          <t>/uploads/fabric/Case/FA8065.jpg</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pepita/FA8074.jpg</t>
+          <t>/uploads/fabric/Case/FA8074.jpg</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pepita/FA8093.jpg</t>
+          <t>/uploads/fabric/Case/FA8093.jpg</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pepita/FA8094.jpg</t>
+          <t>/uploads/fabric/Case/FA8094.jpg</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
+          <t>/uploads/fabric/Case/FA3018.jpg</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pinstripe/FA3055.jpg</t>
+          <t>/uploads/fabric/Case/FA3055.jpg</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pinstripe/FA3067.jpg</t>
+          <t>/uploads/fabric/Case/FA3067.jpg</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Pinstripe/FA3074.jpg</t>
+          <t>/uploads/fabric/Case/FA3074.jpg</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
+          <t>/uploads/fabric/Case/FA8525.jpg</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+          <t>/uploads/fabric/Case/FA3132.jpg</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
+          <t>/uploads/fabric/Case/FA3217.jpg</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
+          <t>/uploads/fabric/Case/FA3258.jpg</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
+          <t>/uploads/fabric/Case/FA3272.jpg</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
+          <t>/uploads/fabric/Case/FA8118.jpg</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Studio /FA8128.jpg</t>
+          <t>/uploads/fabric/Case/FA8128.jpg</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Studio /FA8165.jpg</t>
+          <t>/uploads/fabric/Case/FA8165.jpg</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
+          <t>/uploads/fabric/Case/FA8166.jpg</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
+          <t>/uploads/fabric/Case/FA8217.jpg</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Tartan/FA8237 Black Watch.jpg</t>
+          <t>/uploads/fabric/Case/FA8237.jpg</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Tartan/FA8271 Mackenzie.jpg</t>
+          <t>/uploads/fabric/Case/FA8271.jpg</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
+          <t>/uploads/fabric/Case/FA8517.jpg</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
+          <t>/uploads/fabric/Case/FA8553.jpg</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+          <t>/uploads/fabric/Case/FA2002.jpg</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+          <t>/uploads/fabric/Case/FA2202.jpg</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
+          <t>/uploads/fabric/Case/FA2729.jpg</t>
         </is>
       </c>
     </row>

--- a/data/import/fabric/fabric.xlsx
+++ b/data/import/fabric/fabric.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="320" yWindow="780" windowWidth="33900" windowHeight="19660" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="product_types" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,18 +16,48 @@
     <sheet name="sku_case_gallery" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -53,11 +82,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,8 +461,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="24.33203125" customWidth="1" min="3" max="3"/>
+    <col width="17.83203125" customWidth="1" min="4" max="4"/>
+    <col width="47.33203125" customWidth="1" min="5" max="5"/>
+    <col width="18.6640625" customWidth="1" min="6" max="6"/>
+    <col width="33.5" customWidth="1" min="7" max="7"/>
+    <col width="17.33203125" customWidth="1" min="8" max="8"/>
+    <col width="38.5" customWidth="1" min="9" max="9"/>
+    <col width="21.83203125" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -485,379 +537,838 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="135" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>bmw-check</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BMW Check</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>BMW CHECK</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Classic Scottish square pattern for BMW Isetta</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>BMW Isetta Classic Tartan Seat Upholstery Fabric</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Authentic flatwoven green Scottish square fabric for BMW Isetta restoration (models up to 1958).Exact OEM match pattern. Inquire for rolls.</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA1836.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>bmw-m-pattern</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BMW M Pattern</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BMW M PATTERN</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>The M-Stripe seat cloth is a  replica of the original material used in the prototype M8.</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>BMW Seat Fabric with Foam</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>Premium reproduction of the iconic M Jahre M-Stripe seat fabric. A replica of the ultra-rare material found in the legendary M8 Prototype cabin.</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA5990.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="L3" s="1" t="n"/>
+      <c r="M3" s="1" t="n"/>
+      <c r="N3" s="1" t="n"/>
+      <c r="O3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="165" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>houndstooth-plaid</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Houndstooth Plaid</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>HOUNDSTOOTH PLAID</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>This textile features an intricate houndstooth-based Glen plaid layout blended with Scottish Squares for seat upholstery</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Houndstooth based Glen plaid with Tartan for Seat Upholstery</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n"/>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Premium automotive seat upholstery featuring an intricate houndstooth-based Glen plaid layout blended with Scottish squares. Perfect for vintage car restoration.</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n"/>
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8765.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="L4" s="1" t="n"/>
+      <c r="M4" s="1" t="n"/>
+      <c r="N4" s="1" t="n"/>
+      <c r="O4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="75" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>mercedes-check</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mercedes Check </t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MERCEDES CHECK </t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>This premium, original-specification automotive interior textile is an authentic factory-match reproduction of the classic first-generation Mercedes-Benz W460 G-Klasse (G-Wagon)</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Vintage Mercedes G-Wagon Seat Upholstery Fabric</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n"/>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>Authentic 1980s Mercedes W460 G-class seat upholstery fabric. Heavy-duty flatwoven Panamabond square design in Beige Black</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="n"/>
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8475.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="L5" s="1" t="n"/>
+      <c r="M5" s="1" t="n"/>
+      <c r="N5" s="1" t="n"/>
+      <c r="O5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>mercedes-rodeo</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mercedes Rodeo</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>MERCEDES RODEO</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>This premium, original-specification automotive interior textile is an authentic factory-match reproduction of the late 1980's Mercedes-Benz G-Klasse. The same pattern is used in 2025 G550 'Stronger Than the 1980s" Special Edition</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n"/>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Mercedes G-Wagon 'Stronger Than the 1980s'  Seat Fabric</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n"/>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Get the look of the limited edition G550 Stronger Than the 1980s cabin. Authentic Mercedes Rodeo Grey-Black cube upholstery fabric</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8598.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="n"/>
+      <c r="N6" s="1" t="n"/>
+      <c r="O6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>mercedes-tartan</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Mercedes Tartan</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>MERCEDES TARTAN</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Woven from 100% pure wool, this elite fabric is engineered exclusively for interior restoration of the legendary Mercedes-Benz W198 300SL Gullwing</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>Mercedes W198 300SL Gullwing 100% Wool Fabric</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n"/>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>Authentic 100% wool 1954-1963 Mercedes-Benz W198 300SL Gullwing seat fabric. Factory-match blue/grey Scottish square tartan</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="n"/>
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8626.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="L7" s="1" t="n"/>
+      <c r="M7" s="1" t="n"/>
+      <c r="N7" s="1" t="n"/>
+      <c r="O7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>porsche-check</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Porsche Check</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE CHECK</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Classic pattern Porsche upholstery fabric</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vintage Porsche Seating Upholstery Fabric </t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vintage Porsche Seating Upholstery Fabric </t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="n"/>
+      <c r="K8" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8045.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="L8" s="1" t="n"/>
+      <c r="M8" s="1" t="n"/>
+      <c r="N8" s="1" t="n"/>
+      <c r="O8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>porsche-herringbone</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Porsche Herringbone</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE HERRINGBONE</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n"/>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>This authentic, OEM-specification automotive seating textile is an exact factory-match reproduction for the upholstery of Porsche 924</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vintage Porsche Seating Upholstery Fabric Herringbone </t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n"/>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>Authentic 1978 Porsche 924 seat upholstery fabric. Premium factory-match Beige Cream Black herringbone textile</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="n"/>
+      <c r="K9" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA3570.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="L9" s="1" t="n"/>
+      <c r="M9" s="1" t="n"/>
+      <c r="N9" s="1" t="n"/>
+      <c r="O9" s="1" t="n"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>porsche-madras</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Porsche Madras</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE MADRAS</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>This is the heritage seat upholstery fabric originally offered by Stuttgart as an exclusive cabin option between 1972 and 1975 used in early G-Model Porsche 911s (including the 911T, E, S, and early Carrera).</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Porsche 911 Madras Seat Upholstery Fabric</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n"/>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Authentic 1972-1975 Porsche 911 Madras seat fabric. Premium factory-match windowpane plaid for vintage F-Model &amp; G-Model Carrera restorations</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="n"/>
+      <c r="K10" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8326.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="L10" s="1" t="n"/>
+      <c r="M10" s="1" t="n"/>
+      <c r="N10" s="1" t="n"/>
+      <c r="O10" s="1" t="n"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>porsche-pepita</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Porsche Pepita</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE PEPITA</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Porsche Pepita is arguably the most famous, style-defining interior textile in sports car history. Officially introduced in 1965 for the original 911, Pepita originated as a special-request option for late-model Porsche 356 classics in the early 1960s.</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Porsche Classic Pepita Fabric | Heritage Design Seat Upholstery</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="n"/>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Authentic black &amp; white Porsche Pepita seat fabric. Premium factory-match pattern for classic 911 restorations and modern Heritage Design upgrades. More colors available.</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="n"/>
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8013.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="L11" s="1" t="n"/>
+      <c r="M11" s="1" t="n"/>
+      <c r="N11" s="1" t="n"/>
+      <c r="O11" s="1" t="n"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>porsche-pinstripe</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Porsche Pinstripe</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE PINSTRIPE</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Porsche Pinstripe is a highly sophisticated, business-suit-inspired executive textile that defined the interiors of late-1970s and 1980s Porsche sports cars. It became a staple option across the air-cooled 911 (G-Model) series and the entire front-engine transaxle family (924, 944, and 928)</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>Vintage Porsche Pinstripe Seat Upholstery Fabric</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>Authentic 1977-1990 Porsche Pinstripe seat fabric. Premium factory-match flannel for classic 911, 924, 928, and 944 cabin restoration.</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA3018.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="1" t="n"/>
+      <c r="N12" s="1" t="n"/>
+      <c r="O12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>porsche-plaid</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Porsche Plaid</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE PLAID</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>This is a premium 100% wool flatwoven plaid fabric replicated for the 1973 Porsche 911 RSR</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n"/>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>Vintage Porsche Blue Plaid Fabric - 100% Wool Flatwoven Twill</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n"/>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>Discover premium 100% wool automotive fabric featuring the classic 1970s Porsche RSR blue tartan pattern. Durable, period-correct woven cloth for luxury interiors.</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="n"/>
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8525.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>porsche-script</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="L13" s="1" t="n"/>
+      <c r="M13" s="1" t="n"/>
+      <c r="N13" s="1" t="n"/>
+      <c r="O13" s="1" t="n"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>porsche-velours-pinstripe</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Porsche Script</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE VELOURS PINSTRIPE</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>It is a velvet-like fabric featuring a dense, cut-pile surface. This gives it an incredibly plush, soft-touch texture that was highly favored for luxury and executive sports car cabins in the 1980s</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n"/>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>Porsche 911 928 944 Pinstripe Velour Seat Cloth</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n"/>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>Vintage-style vertical pinstripe velour fabric for classic Porsche interiors. Perfect for high-end seat insert and door card restorations.</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="n"/>
+      <c r="K14" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA3132.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="L14" s="1" t="n"/>
+      <c r="M14" s="1" t="n"/>
+      <c r="N14" s="1" t="n"/>
+      <c r="O14" s="1" t="n"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>porsche-studio</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Porsche Studio </t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE STUDIO</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>This is an authentic reproduction of Porsche’s iconic "Studio Check" automotive upholstery fabric, specifically curated for  Porsche 911 Carrera (964/993 generations), Porsche 928, and Porsche 968</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n"/>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>Porsche Studio Check Grey Fabric | 964 993 928 Restoration Cloth</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n"/>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>Vintage Authentic reproduction of the classic Porsche Studio Check upholstery fabric</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="n"/>
+      <c r="K15" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8118.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="L15" s="1" t="n"/>
+      <c r="M15" s="1" t="n"/>
+      <c r="N15" s="1" t="n"/>
+      <c r="O15" s="1" t="n"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>porsche-tartan</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Porsche Tartan</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>PORSCHE TARTAN</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Introduced in 1975, this legendary pattern was famously optioned on the early Porsche 911 Turbo (930) and the 911SC</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n"/>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>Porsche Classic Tartan Fabric | 911SC &amp; 930 Turbo Seat Cloth</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="n"/>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>Vintage-style  plaid upholstery cloth for classic Porsche interiors. Durable, period-correct flatwoven check fabric for seats and door cards.</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="n"/>
+      <c r="K16" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8217.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="L16" s="1" t="n"/>
+      <c r="M16" s="1" t="n"/>
+      <c r="N16" s="1" t="n"/>
+      <c r="O16" s="1" t="n"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>selected-plaid</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Selected Plaid</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>SELETED PLAID</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Selected plaid for automotive seat upholstery</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n"/>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automotive Plaid for Seat Upholstery </t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n"/>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Polyester automtive plaid for seat upholstery </t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="n"/>
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8517.jpg</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="L17" s="1" t="n"/>
+      <c r="M17" s="1" t="n"/>
+      <c r="N17" s="1" t="n"/>
+      <c r="O17" s="1" t="n"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>spirit-of-le-mans</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Spirit of Le Mans</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>SPIRIT OF LE MANS</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>The Spirit of Le Mans (SOLM) Wool Line is a premium, motorsport-inspired tartan collection woven in Scotland and engineered specifically for high-end automotive interiors. 100% premium wool woven in a durable 2/2 twill, featuring a heavy-duty weight of 500 glm (365 gsm). Pre-treated with specialized Soil Resist and Fire Retardant (FR) compliance coatings tailored for automotive safety standards.</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n"/>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>100% Luxury Wool Automotive Fabric | Fire Retardant Tartan</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="n"/>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>Heavyweight wool racing tartan cloth for luxury car interiors. Pre-treated with fire-retardant and soil-resist coatings. Woven in Scotland</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="n"/>
+      <c r="K18" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA2002.jpg</t>
         </is>
       </c>
+      <c r="L18" s="1" t="n"/>
+      <c r="M18" s="1" t="n"/>
+      <c r="N18" s="1" t="n"/>
+      <c r="O18" s="1" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="1" t="n"/>
+      <c r="E19" s="1" t="n"/>
+      <c r="F19" s="1" t="n"/>
+      <c r="G19" s="1" t="n"/>
+      <c r="H19" s="1" t="n"/>
+      <c r="I19" s="1" t="n"/>
+      <c r="J19" s="1" t="n"/>
+      <c r="K19" s="1" t="n"/>
+      <c r="L19" s="1" t="n"/>
+      <c r="M19" s="1" t="n"/>
+      <c r="N19" s="1" t="n"/>
+      <c r="O19" s="1" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="1" t="n"/>
+      <c r="D20" s="1" t="n"/>
+      <c r="E20" s="1" t="n"/>
+      <c r="F20" s="1" t="n"/>
+      <c r="G20" s="1" t="n"/>
+      <c r="H20" s="1" t="n"/>
+      <c r="I20" s="1" t="n"/>
+      <c r="J20" s="1" t="n"/>
+      <c r="K20" s="1" t="n"/>
+      <c r="L20" s="1" t="n"/>
+      <c r="M20" s="1" t="n"/>
+      <c r="N20" s="1" t="n"/>
+      <c r="O20" s="1" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="1" t="n"/>
+      <c r="D21" s="1" t="n"/>
+      <c r="E21" s="1" t="n"/>
+      <c r="F21" s="1" t="n"/>
+      <c r="G21" s="1" t="n"/>
+      <c r="H21" s="1" t="n"/>
+      <c r="I21" s="1" t="n"/>
+      <c r="J21" s="1" t="n"/>
+      <c r="K21" s="1" t="n"/>
+      <c r="L21" s="1" t="n"/>
+      <c r="M21" s="1" t="n"/>
+      <c r="N21" s="1" t="n"/>
+      <c r="O21" s="1" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
+      <c r="D22" s="1" t="n"/>
+      <c r="E22" s="1" t="n"/>
+      <c r="F22" s="1" t="n"/>
+      <c r="G22" s="1" t="n"/>
+      <c r="H22" s="1" t="n"/>
+      <c r="I22" s="1" t="n"/>
+      <c r="J22" s="1" t="n"/>
+      <c r="K22" s="1" t="n"/>
+      <c r="L22" s="1" t="n"/>
+      <c r="M22" s="1" t="n"/>
+      <c r="N22" s="1" t="n"/>
+      <c r="O22" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -870,8 +1381,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H86"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="34.1640625" customWidth="1" min="1" max="1"/>
+    <col width="15.83203125" customWidth="1" min="2" max="2"/>
+    <col width="19.33203125" customWidth="1" min="3" max="3"/>
+    <col width="22.1640625" customWidth="1" min="4" max="4"/>
+    <col width="17.6640625" customWidth="1" min="5" max="5"/>
+    <col width="19.83203125" customWidth="1" min="7" max="7"/>
+    <col width="24.33203125" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -912,6 +1432,2641 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>default_value_ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bmw-check</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.6mm</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.6mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bmw-m-pattern</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.0mm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2.0mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Polyester</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>houndstooth-plaid</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.8mm</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.8mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mercedes-check</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.3mm</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.3mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mercedes-rodeo</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Polyester</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mercedes-tartan</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.8mm</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0.8mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Wool</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ウール</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1.3mm</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1.3mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>porsche-herringbone</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1.2mm</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1.2mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>porsche-madras</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.1mm</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1.1mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1.1mm</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1.1mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1.6mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>porsche-plaid</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Wool</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ウール</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>porsche-velours-pinstripe</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1.6mm</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.3mm</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.3mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1.3mm</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.3mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>4</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>5</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>selected-plaid</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Polyester</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0.6mm</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>0.6mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Wool</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ウール</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>イギリス</t>
         </is>
       </c>
     </row>
@@ -927,7 +4082,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -963,7 +4118,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1009,7 +4164,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="20.1640625" customWidth="1" min="3" max="3"/>
+    <col width="36.83203125" customWidth="1" min="5" max="5"/>
+    <col width="21.33203125" customWidth="1" min="6" max="6"/>
+    <col width="35.83203125" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="30.1640625" customWidth="1" min="12" max="13"/>
+    <col width="21.83203125" customWidth="1" min="14" max="14"/>
+    <col width="22.33203125" customWidth="1" min="15" max="15"/>
+    <col width="36.6640625" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1119,6 +4285,11 @@
           <t>FA1836</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BLACK/GRAY/BROWN</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>/uploads/fabric/BMW Check/FA1836.jpg</t>
@@ -1161,6 +4332,11 @@
           <t>FA5990</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>M PATTERN</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>/uploads/fabric/BMW M Pattern/FA5990.jpg</t>
@@ -1203,6 +4379,11 @@
           <t>FA8765</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GRAY/WHITE/BROWN</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>/uploads/fabric/Houndstooth Plaid/FA8765.jpg</t>
@@ -1245,6 +4426,11 @@
           <t>FA8475</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BLACK/BROWN/RED</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>/uploads/fabric/Mercedes Check /FA8475.jpg</t>
@@ -1287,6 +4473,11 @@
           <t>FA8598</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GRAY/BLACK</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>/uploads/fabric/Mercedes Rodeo/FA8598.jpg</t>
@@ -1329,6 +4520,11 @@
           <t>FA8626</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BLUE/GRAY</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>/uploads/fabric/Mercedes Tartan/FA8626.jpg</t>
@@ -1371,6 +4567,11 @@
           <t>FA8637</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GREEN/GRAY/WHITE</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>/uploads/fabric/Mercedes Tartan/FA8637.jpg</t>
@@ -1413,6 +4614,11 @@
           <t>FA8045</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BLACK/BROWN/YELLOW</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Check/FA8045.jpg</t>
@@ -1455,6 +4661,11 @@
           <t>FA8057</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BROWN/TAN/GREEN</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Check/FA8057.jpg</t>
@@ -1497,6 +4708,11 @@
           <t>FA8063</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE/RED</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Check/FA8063.jpg</t>
@@ -1539,6 +4755,11 @@
           <t>FA3570</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Herringbone/FA3570.jpg</t>
@@ -1581,6 +4802,11 @@
           <t>FA8326</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BLUE/WHITE</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Madras/FA8326.jpg</t>
@@ -1623,6 +4849,11 @@
           <t>FA8354</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ORANGE/BROWN</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Madras/FA8354.jpg</t>
@@ -1665,6 +4896,11 @@
           <t>FA8013</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE/ORANGE</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8013.jpg</t>
@@ -1707,6 +4943,11 @@
           <t>FA8026</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE/BLUE</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8026.jpg</t>
@@ -1749,6 +4990,11 @@
           <t>FA8065</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8065.jpg</t>
@@ -1791,6 +5037,11 @@
           <t>FA8074</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE/BEIGE</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8074.jpg</t>
@@ -1833,6 +5084,11 @@
           <t>FA8093</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE/GREEN</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8093.jpg</t>
@@ -1875,6 +5131,11 @@
           <t>FA8094</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE/RED</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pepita/FA8094.jpg</t>
@@ -1917,6 +5178,11 @@
           <t>FA3018</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BURGUNDY/WHITE</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pinstripe/FA3018.jpg</t>
@@ -1959,6 +5225,11 @@
           <t>FA3055</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MAROON/WHITE</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pinstripe/FA3055.jpg</t>
@@ -2001,6 +5272,11 @@
           <t>FA3067</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BLACK/DARK GRAY/GRAY</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pinstripe/FA3067.jpg</t>
@@ -2043,6 +5319,11 @@
           <t>FA3074</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Pinstripe/FA3074.jpg</t>
@@ -2085,6 +5366,11 @@
           <t>FA8525</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>BLUE/BLACK/WHITE/RED</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Plaid/FA8525.jpg</t>
@@ -2119,7 +5405,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>porsche-script</t>
+          <t>porsche-pinstripe</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2127,14 +5413,19 @@
           <t>FA3132</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GRAY/BLUE</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3132.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3132.jpg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2144,7 +5435,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3132.jpg</t>
+          <t>/uploads/fabric/Porsche Pinstripe/FA3132.jpg</t>
         </is>
       </c>
     </row>
@@ -2161,7 +5452,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>porsche-script</t>
+          <t>porsche-velours-pinstripe</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2169,14 +5460,19 @@
           <t>FA3217</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BLACK/RED</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3217.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3217.jpg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2186,7 +5482,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3217.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3217.jpg</t>
         </is>
       </c>
     </row>
@@ -2203,7 +5499,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>porsche-script</t>
+          <t>porsche-velours-pinstripe</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2211,14 +5507,19 @@
           <t>FA3258</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BROWN/WHITE</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3258.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3258.jpg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2228,7 +5529,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3258.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3258.jpg</t>
         </is>
       </c>
     </row>
@@ -2245,7 +5546,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>porsche-script</t>
+          <t>porsche-velours-pinstripe</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2253,14 +5554,19 @@
           <t>FA3272</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GRAY/WHITE</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3272.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3272.jpg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2270,7 +5576,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Porsche Script/FA3272.jpg</t>
+          <t>/uploads/fabric/Porsche Velcours Pinstripe/FA3272.jpg</t>
         </is>
       </c>
     </row>
@@ -2295,6 +5601,11 @@
           <t>FA8118</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RED/MAROON</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8118.jpg</t>
@@ -2337,6 +5648,11 @@
           <t>FA8128</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NAVY/BLUE/BLACK</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8128.jpg</t>
@@ -2379,6 +5695,11 @@
           <t>FA8165</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>GRAY</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8165.jpg</t>
@@ -2421,6 +5742,11 @@
           <t>FA8166</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GRAY</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Studio /FA8166.jpg</t>
@@ -2463,6 +5789,11 @@
           <t>FA8217</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BLUE/RED/BLACK</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Tartan/FA8217 McLaughli.jpg</t>
@@ -2505,6 +5836,11 @@
           <t>FA8237</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>NAVY/BLUE/BLACK</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Tartan/FA8237 Black Watch.jpg</t>
@@ -2547,6 +5883,11 @@
           <t>FA8271</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GRAY/BLUE/WHITE</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>/uploads/fabric/Porsche Tartan/FA8271 Mackenzie.jpg</t>
@@ -2589,6 +5930,11 @@
           <t>FA8517</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BLACK/RED/BLUE</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
@@ -2631,6 +5977,11 @@
           <t>FA8553</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BLUE/NAVY/ORANGE</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
@@ -2673,6 +6024,11 @@
           <t>FA2002</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BLUE/NAVY/RED</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
@@ -2715,6 +6071,11 @@
           <t>FA2202</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BLUE/ORANGE/NAVY</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
@@ -2755,6 +6116,11 @@
       <c r="D41" t="inlineStr">
         <is>
           <t>FA2729</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BLUE/BLACK/RED</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2790,7 +6156,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2836,7 +6202,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2892,7 +6258,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/data/import/fabric/fabric.xlsx
+++ b/data/import/fabric/fabric.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="320" yWindow="780" windowWidth="33900" windowHeight="19660" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="300" yWindow="780" windowWidth="33900" windowHeight="19660" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="product_types" sheetId="1" state="visible" r:id="rId1"/>
@@ -1114,7 +1114,7 @@
       <c r="J14" s="1" t="n"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Cover/FA3132.jpg</t>
+          <t>/uploads/fabric/Cover/FA3217.jpg</t>
         </is>
       </c>
       <c r="L14" s="1" t="n"/>
@@ -1471,6 +1471,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bmw-check</t>
+        </is>
+      </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
@@ -1501,6 +1506,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bmw-check</t>
+        </is>
+      </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
@@ -1531,6 +1541,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bmw-check</t>
+        </is>
+      </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
@@ -1561,6 +1576,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bmw-check</t>
+        </is>
+      </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
@@ -1626,6 +1646,11 @@
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bmw-m-pattern</t>
+        </is>
+      </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
@@ -1656,6 +1681,11 @@
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bmw-m-pattern</t>
+        </is>
+      </c>
       <c r="B9" t="n">
         <v>3</v>
       </c>
@@ -1686,6 +1716,11 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bmw-m-pattern</t>
+        </is>
+      </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
@@ -1716,6 +1751,11 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bmw-m-pattern</t>
+        </is>
+      </c>
       <c r="B11" t="n">
         <v>5</v>
       </c>
@@ -1781,6 +1821,11 @@
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>houndstooth-plaid</t>
+        </is>
+      </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
@@ -1811,6 +1856,11 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>houndstooth-plaid</t>
+        </is>
+      </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
@@ -1841,6 +1891,11 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>houndstooth-plaid</t>
+        </is>
+      </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
@@ -1871,6 +1926,11 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>houndstooth-plaid</t>
+        </is>
+      </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
@@ -1936,6 +1996,11 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mercedes-check</t>
+        </is>
+      </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
@@ -1966,6 +2031,11 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mercedes-check</t>
+        </is>
+      </c>
       <c r="B19" t="n">
         <v>3</v>
       </c>
@@ -1996,6 +2066,11 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mercedes-check</t>
+        </is>
+      </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
@@ -2026,6 +2101,11 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mercedes-check</t>
+        </is>
+      </c>
       <c r="B21" t="n">
         <v>5</v>
       </c>
@@ -2091,6 +2171,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mercedes-rodeo</t>
+        </is>
+      </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
@@ -2121,6 +2206,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mercedes-rodeo</t>
+        </is>
+      </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
@@ -2151,6 +2241,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mercedes-rodeo</t>
+        </is>
+      </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
@@ -2181,6 +2276,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mercedes-rodeo</t>
+        </is>
+      </c>
       <c r="B26" t="n">
         <v>5</v>
       </c>
@@ -2246,6 +2346,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mercedes-tartan</t>
+        </is>
+      </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
@@ -2276,6 +2381,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mercedes-tartan</t>
+        </is>
+      </c>
       <c r="B29" t="n">
         <v>3</v>
       </c>
@@ -2306,6 +2416,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mercedes-tartan</t>
+        </is>
+      </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
@@ -2336,6 +2451,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mercedes-tartan</t>
+        </is>
+      </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
@@ -2401,6 +2521,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
@@ -2431,6 +2556,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
@@ -2461,6 +2591,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
@@ -2491,6 +2626,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>porsche-check</t>
+        </is>
+      </c>
       <c r="B36" t="n">
         <v>5</v>
       </c>
@@ -2556,6 +2696,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>porsche-herringbone</t>
+        </is>
+      </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
@@ -2586,6 +2731,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>porsche-herringbone</t>
+        </is>
+      </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
@@ -2616,6 +2766,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>porsche-herringbone</t>
+        </is>
+      </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
@@ -2646,6 +2801,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>porsche-herringbone</t>
+        </is>
+      </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
@@ -2711,6 +2871,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>porsche-madras</t>
+        </is>
+      </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
@@ -2741,6 +2906,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>porsche-madras</t>
+        </is>
+      </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
@@ -2771,6 +2941,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>porsche-madras</t>
+        </is>
+      </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
@@ -2801,6 +2976,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>porsche-madras</t>
+        </is>
+      </c>
       <c r="B46" t="n">
         <v>5</v>
       </c>
@@ -2866,6 +3046,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
@@ -2896,6 +3081,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
       <c r="B49" t="n">
         <v>3</v>
       </c>
@@ -2926,6 +3116,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
@@ -2956,6 +3151,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>porsche-pepita</t>
+        </is>
+      </c>
       <c r="B51" t="n">
         <v>5</v>
       </c>
@@ -3021,6 +3221,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
@@ -3051,6 +3256,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
       <c r="B54" t="n">
         <v>3</v>
       </c>
@@ -3081,6 +3291,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
@@ -3111,6 +3326,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>porsche-pinstripe</t>
+        </is>
+      </c>
       <c r="B56" t="n">
         <v>5</v>
       </c>
@@ -3176,6 +3396,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>porsche-plaid</t>
+        </is>
+      </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
@@ -3206,6 +3431,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>porsche-plaid</t>
+        </is>
+      </c>
       <c r="B59" t="n">
         <v>3</v>
       </c>
@@ -3236,6 +3466,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>porsche-plaid</t>
+        </is>
+      </c>
       <c r="B60" t="n">
         <v>4</v>
       </c>
@@ -3266,6 +3501,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>porsche-plaid</t>
+        </is>
+      </c>
       <c r="B61" t="n">
         <v>5</v>
       </c>
@@ -3331,6 +3571,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>porsche-velours-pinstripe</t>
+        </is>
+      </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
@@ -3361,6 +3606,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>porsche-velours-pinstripe</t>
+        </is>
+      </c>
       <c r="B64" t="n">
         <v>3</v>
       </c>
@@ -3391,6 +3641,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>porsche-velours-pinstripe</t>
+        </is>
+      </c>
       <c r="B65" t="n">
         <v>4</v>
       </c>
@@ -3421,6 +3676,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>porsche-velours-pinstripe</t>
+        </is>
+      </c>
       <c r="B66" t="n">
         <v>5</v>
       </c>
@@ -3486,6 +3746,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
@@ -3516,6 +3781,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
       <c r="B69" t="n">
         <v>3</v>
       </c>
@@ -3546,6 +3816,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
@@ -3576,6 +3851,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>porsche-studio</t>
+        </is>
+      </c>
       <c r="B71" t="n">
         <v>5</v>
       </c>
@@ -3641,6 +3921,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
@@ -3671,6 +3956,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
       <c r="B74" t="n">
         <v>3</v>
       </c>
@@ -3701,6 +3991,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
       <c r="B75" t="n">
         <v>4</v>
       </c>
@@ -3731,6 +4026,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>porsche-tartan</t>
+        </is>
+      </c>
       <c r="B76" t="n">
         <v>5</v>
       </c>
@@ -3796,6 +4096,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>selected-plaid</t>
+        </is>
+      </c>
       <c r="B78" t="n">
         <v>2</v>
       </c>
@@ -3826,6 +4131,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>selected-plaid</t>
+        </is>
+      </c>
       <c r="B79" t="n">
         <v>3</v>
       </c>
@@ -3856,6 +4166,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>selected-plaid</t>
+        </is>
+      </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
@@ -3886,6 +4201,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>selected-plaid</t>
+        </is>
+      </c>
       <c r="B81" t="n">
         <v>5</v>
       </c>
@@ -3951,6 +4271,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
@@ -3981,6 +4306,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
       <c r="B84" t="n">
         <v>3</v>
       </c>
@@ -4011,6 +4341,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
       <c r="B85" t="n">
         <v>4</v>
       </c>
@@ -4041,6 +4376,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
       <c r="B86" t="n">
         <v>5</v>
       </c>

--- a/data/import/fabric/fabric.xlsx
+++ b/data/import/fabric/fabric.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="300" yWindow="780" windowWidth="33900" windowHeight="19660" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="300" yWindow="780" windowWidth="33900" windowHeight="19660" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="product_types" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="product_type_specs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="product_type_certifications" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="product_type_maintenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="skus" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sku_specs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="product_type_downloads" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="sku_case_gallery" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_types" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_type_specs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_type_certifications" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_type_maintenance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skus" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sku_specs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_type_downloads" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sku_case_gallery" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -461,11 +461,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="24.33203125" customWidth="1" min="3" max="3"/>
+    <col width="25.6640625" customWidth="1" min="3" max="3"/>
     <col width="17.83203125" customWidth="1" min="4" max="4"/>
     <col width="47.33203125" customWidth="1" min="5" max="5"/>
     <col width="18.6640625" customWidth="1" min="6" max="6"/>
@@ -473,6 +473,7 @@
     <col width="17.33203125" customWidth="1" min="8" max="8"/>
     <col width="38.5" customWidth="1" min="9" max="9"/>
     <col width="21.83203125" customWidth="1" min="10" max="10"/>
+    <col width="44.1640625" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,25 +554,41 @@
           <t>BMW CHECK</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n"/>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>BMW チェック</t>
+        </is>
+      </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Classic Scottish square pattern for BMW Isetta</t>
         </is>
       </c>
-      <c r="F2" s="1" t="n"/>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>BMWイセッタ向けのクラシックなスコットランドスクエアパターン。</t>
+        </is>
+      </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
           <t>BMW Isetta Classic Tartan Seat Upholstery Fabric</t>
         </is>
       </c>
-      <c r="H2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>BMWイセッタ クラシックタータン シート張り地</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Authentic flatwoven green Scottish square fabric for BMW Isetta restoration (models up to 1958).Exact OEM match pattern. Inquire for rolls.</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>BMWイセッタ（1958年以前モデル）レストア用の本格的なフラットウィーブングリーンスコットランドスクエアファブリック。純正OEMマッチパターン。ロールでのお問い合わせ承ります。</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA1836.jpg</t>
@@ -598,25 +615,41 @@
           <t>BMW M PATTERN</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n"/>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>BMW M パターン</t>
+        </is>
+      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t>The M-Stripe seat cloth is a  replica of the original material used in the prototype M8.</t>
         </is>
       </c>
-      <c r="F3" s="1" t="n"/>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Mストライプシートクロスは、プロトタイプM8に使用されたオリジナル素材のレプリカです。</t>
+        </is>
+      </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
           <t>BMW Seat Fabric with Foam</t>
         </is>
       </c>
-      <c r="H3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>BMW Mシートファブリック（フォーム付き）</t>
+        </is>
+      </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Premium reproduction of the iconic M Jahre M-Stripe seat fabric. A replica of the ultra-rare material found in the legendary M8 Prototype cabin.</t>
         </is>
       </c>
-      <c r="J3" s="1" t="n"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>象徴的なMヤーレMストライプシート生地のプレミアム復刻版。伝説のM8プロトタイプキャビンに使用された超希少素材のレプリカ。</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA5990.jpg</t>
@@ -643,25 +676,41 @@
           <t>HOUNDSTOOTH PLAID</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>ハウンドトゥース プレイド</t>
+        </is>
+      </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
           <t>This textile features an intricate houndstooth-based Glen plaid layout blended with Scottish Squares for seat upholstery</t>
         </is>
       </c>
-      <c r="F4" s="1" t="n"/>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>千鳥格子ベースのグレンチェックにスコティッシュスクエアを組み合わせた複雑なレイアウトのシート張り地。</t>
+        </is>
+      </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Houndstooth based Glen plaid with Tartan for Seat Upholstery</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n"/>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>千鳥格子ベース グレンチェック×タータン シート張り地</t>
+        </is>
+      </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Premium automotive seat upholstery featuring an intricate houndstooth-based Glen plaid layout blended with Scottish squares. Perfect for vintage car restoration.</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n"/>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>千鳥格子ベースのグレンチェックレイアウトにスコティッシュスクエアを融合させたプレミアム自動車用シート張り地。ヴィンテージカーレストアに最適。</t>
+        </is>
+      </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8765.jpg</t>
@@ -688,25 +737,41 @@
           <t xml:space="preserve">MERCEDES CHECK </t>
         </is>
       </c>
-      <c r="D5" s="1" t="n"/>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>メルセデス チェック</t>
+        </is>
+      </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
           <t>This premium, original-specification automotive interior textile is an authentic factory-match reproduction of the classic first-generation Mercedes-Benz W460 G-Klasse (G-Wagon)</t>
         </is>
       </c>
-      <c r="F5" s="1" t="n"/>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>初代メルセデス・ベンツ W460 Gクラス（G-Wagon）のクラシックな内装を忠実に再現した、プレミアムな純正スペックの自動車用内装テキスタイル。</t>
+        </is>
+      </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Vintage Mercedes G-Wagon Seat Upholstery Fabric</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n"/>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>ヴィンテージ メルセデス G-Wagon シート張り地</t>
+        </is>
+      </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
           <t>Authentic 1980s Mercedes W460 G-class seat upholstery fabric. Heavy-duty flatwoven Panamabond square design in Beige Black</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n"/>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>1980年代メルセデス W460 Gクラス純正シート張り地。ベージュブラックのヘビーデューティーフラットウィーブンパナマボンドスクエアデザイン。</t>
+        </is>
+      </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8475.jpg</t>
@@ -733,25 +798,41 @@
           <t>MERCEDES RODEO</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n"/>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>メルセデス ロデオ</t>
+        </is>
+      </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
           <t>This premium, original-specification automotive interior textile is an authentic factory-match reproduction of the late 1980's Mercedes-Benz G-Klasse. The same pattern is used in 2025 G550 'Stronger Than the 1980s" Special Edition</t>
         </is>
       </c>
-      <c r="F6" s="1" t="n"/>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>1980年代後半のメルセデス・ベンツ Gクラスを忠実に再現したプレミアムな純正スペックファブリック。2025年G550「Stronger Than the 1980s」特別仕様車と同パターン。</t>
+        </is>
+      </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
           <t>Mercedes G-Wagon 'Stronger Than the 1980s'  Seat Fabric</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n"/>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>メルセデス G-Wagon「Stronger Than the 1980s」シート生地</t>
+        </is>
+      </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
           <t>Get the look of the limited edition G550 Stronger Than the 1980s cabin. Authentic Mercedes Rodeo Grey-Black cube upholstery fabric</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n"/>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>限定版G550 Stronger Than the 1980sキャビンの外観を実現。本格的なメルセデスロデオグレーブラックキューブ張り地。</t>
+        </is>
+      </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8598.jpg</t>
@@ -778,25 +859,41 @@
           <t>MERCEDES TARTAN</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n"/>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>メルセデス タータン</t>
+        </is>
+      </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Woven from 100% pure wool, this elite fabric is engineered exclusively for interior restoration of the legendary Mercedes-Benz W198 300SL Gullwing</t>
         </is>
       </c>
-      <c r="F7" s="1" t="n"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>伝説のメルセデス・ベンツ W198 300SL ガルウィングの内装レストア専用に織られた、100%ピュアウールのエリートファブリック。</t>
+        </is>
+      </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
           <t>Mercedes W198 300SL Gullwing 100% Wool Fabric</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n"/>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>メルセデス W198 300SL ガルウィング 100%ウール生地</t>
+        </is>
+      </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
           <t>Authentic 100% wool 1954-1963 Mercedes-Benz W198 300SL Gullwing seat fabric. Factory-match blue/grey Scottish square tartan</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n"/>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>1954-1963年メルセデス・ベンツ W198 300SLガルウィング用本格的な100%ウールシート生地。純正マッチのブルー/グレースコティッシュスクエアタータン。</t>
+        </is>
+      </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8626.jpg</t>
@@ -823,25 +920,41 @@
           <t>PORSCHE CHECK</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n"/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ チェック</t>
+        </is>
+      </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Classic pattern Porsche upholstery fabric</t>
         </is>
       </c>
-      <c r="F8" s="1" t="n"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>クラシックパターンのポルシェ張り地。</t>
+        </is>
+      </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Vintage Porsche Seating Upholstery Fabric </t>
         </is>
       </c>
-      <c r="H8" s="1" t="n"/>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>ヴィンテージ ポルシェ シート張り地</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Vintage Porsche Seating Upholstery Fabric </t>
         </is>
       </c>
-      <c r="J8" s="1" t="n"/>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>ヴィンテージポルシェシート張り地。</t>
+        </is>
+      </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8045.jpg</t>
@@ -868,25 +981,41 @@
           <t>PORSCHE HERRINGBONE</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n"/>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ ヘリンボーン</t>
+        </is>
+      </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
           <t>This authentic, OEM-specification automotive seating textile is an exact factory-match reproduction for the upholstery of Porsche 924</t>
         </is>
       </c>
-      <c r="F9" s="1" t="n"/>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ924の張り地を忠実に再現した、本格的なOEMスペックの自動車用シートテキスタイル。</t>
+        </is>
+      </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Vintage Porsche Seating Upholstery Fabric Herringbone </t>
         </is>
       </c>
-      <c r="H9" s="1" t="n"/>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>ヴィンテージ ポルシェ ヘリンボーン シート張り地</t>
+        </is>
+      </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
           <t>Authentic 1978 Porsche 924 seat upholstery fabric. Premium factory-match Beige Cream Black herringbone textile</t>
         </is>
       </c>
-      <c r="J9" s="1" t="n"/>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>1978年ポルシェ924純正シート張り地。ベージュクリームブラックのヘリンボーンテキスタイル、プレミアムな純正マッチ復刻版。</t>
+        </is>
+      </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA3570.jpg</t>
@@ -913,25 +1042,41 @@
           <t>PORSCHE MADRAS</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n"/>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ マドラス</t>
+        </is>
+      </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
           <t>This is the heritage seat upholstery fabric originally offered by Stuttgart as an exclusive cabin option between 1972 and 1975 used in early G-Model Porsche 911s (including the 911T, E, S, and early Carrera).</t>
         </is>
       </c>
-      <c r="F10" s="1" t="n"/>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>1972年から1975年にかけてシュトゥットガルトが限定キャビンオプションとして提供した、ヘリテージシート張り地。アーリーGモデル ポルシェ911（911T、E、S、アーリーカレラ）に採用。</t>
+        </is>
+      </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
           <t>Porsche 911 Madras Seat Upholstery Fabric</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n"/>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ911 マドラス シート張り地</t>
+        </is>
+      </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
           <t>Authentic 1972-1975 Porsche 911 Madras seat fabric. Premium factory-match windowpane plaid for vintage F-Model &amp; G-Model Carrera restorations</t>
         </is>
       </c>
-      <c r="J10" s="1" t="n"/>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>1972-1975年ポルシェ911マドラス純正シート生地。ヴィンテージFモデル＆Gモデルカレラレストア向けプレミアム純正マッチウィンドウペーンプレイド。</t>
+        </is>
+      </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8326.jpg</t>
@@ -958,25 +1103,41 @@
           <t>PORSCHE PEPITA</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n"/>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ ペピータ</t>
+        </is>
+      </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Porsche Pepita is arguably the most famous, style-defining interior textile in sports car history. Officially introduced in 1965 for the original 911, Pepita originated as a special-request option for late-model Porsche 356 classics in the early 1960s.</t>
         </is>
       </c>
-      <c r="F11" s="1" t="n"/>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>スポーツカーの歴史上最も有名でスタイルを定義した内装テキスタイル。1965年にオリジナル911向けに正式導入され、1960年代初頭の後期ポルシェ356クラシックの特別リクエストオプションとして誕生。</t>
+        </is>
+      </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Porsche Classic Pepita Fabric | Heritage Design Seat Upholstery</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n"/>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ クラシック ペピータ生地 | ヘリテージデザイン シート張り地</t>
+        </is>
+      </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Authentic black &amp; white Porsche Pepita seat fabric. Premium factory-match pattern for classic 911 restorations and modern Heritage Design upgrades. More colors available.</t>
         </is>
       </c>
-      <c r="J11" s="1" t="n"/>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>本格的なブラック＆ホワイトのポルシェペピータシート生地。クラシック911レストアおよびモダンヘリテージデザインアップグレード向けプレミアム純正マッチパターン。その他カラーも承ります。</t>
+        </is>
+      </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8013.jpg</t>
@@ -1003,25 +1164,41 @@
           <t>PORSCHE PINSTRIPE</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n"/>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ ピンストライプ</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Porsche Pinstripe is a highly sophisticated, business-suit-inspired executive textile that defined the interiors of late-1970s and 1980s Porsche sports cars. It became a staple option across the air-cooled 911 (G-Model) series and the entire front-engine transaxle family (924, 944, and 928)</t>
         </is>
       </c>
-      <c r="F12" s="1" t="n"/>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>1970年代後半から1980年代のポルシェスポーツカーの内装を定義した、ビジネススーツに着想を得た非常に洗練されたエグゼクティブテキスタイル。空冷911（Gモデル）シリーズとフロントエンジントランスアクスルファミリー（924、944、928）全体で定番オプションに。</t>
+        </is>
+      </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
           <t>Vintage Porsche Pinstripe Seat Upholstery Fabric</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n"/>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>ヴィンテージ ポルシェ ピンストライプ シート張り地</t>
+        </is>
+      </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
           <t>Authentic 1977-1990 Porsche Pinstripe seat fabric. Premium factory-match flannel for classic 911, 924, 928, and 944 cabin restoration.</t>
         </is>
       </c>
-      <c r="J12" s="1" t="n"/>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>1977-1990年ポルシェピンストライプ純正シート生地。クラシック911、924、928、944キャビンレストア向けプレミアム純正マッチフランネル。</t>
+        </is>
+      </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA3018.jpg</t>
@@ -1048,25 +1225,41 @@
           <t>PORSCHE PLAID</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n"/>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ プレイド</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
           <t>This is a premium 100% wool flatwoven plaid fabric replicated for the 1973 Porsche 911 RSR</t>
         </is>
       </c>
-      <c r="F13" s="1" t="n"/>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>1973年ポルシェ911 RSR向けに再現された、プレミアムな100%ウールフラットウーブンプレイドファブリック。</t>
+        </is>
+      </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
           <t>Vintage Porsche Blue Plaid Fabric - 100% Wool Flatwoven Twill</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n"/>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>ヴィンテージ ポルシェ ブループレイド生地 - 100%ウール フラットウーブンツイル</t>
+        </is>
+      </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
           <t>Discover premium 100% wool automotive fabric featuring the classic 1970s Porsche RSR blue tartan pattern. Durable, period-correct woven cloth for luxury interiors.</t>
         </is>
       </c>
-      <c r="J13" s="1" t="n"/>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>クラシックな1970年代ポルシェRSRブルータータンパターンを特徴とするプレミアム100%ウール自動車用生地。高級内装向けの耐久性のある時代考証織物。</t>
+        </is>
+      </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8525.jpg</t>
@@ -1093,25 +1286,41 @@
           <t>PORSCHE VELOURS PINSTRIPE</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n"/>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ ベロア ピンストライプ</t>
+        </is>
+      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
           <t>It is a velvet-like fabric featuring a dense, cut-pile surface. This gives it an incredibly plush, soft-touch texture that was highly favored for luxury and executive sports car cabins in the 1980s</t>
         </is>
       </c>
-      <c r="F14" s="1" t="n"/>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>高密度なカットパイル表面を持つベルベットのような生地。1980年代の高級車およびエグゼクティブスポーツカーキャビンで高く評価された、非常に豪華でソフトなタッチのテクスチャー。</t>
+        </is>
+      </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
           <t>Porsche 911 928 944 Pinstripe Velour Seat Cloth</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n"/>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ911 928 944 ピンストライプ ベロア シートクロス</t>
+        </is>
+      </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
           <t>Vintage-style vertical pinstripe velour fabric for classic Porsche interiors. Perfect for high-end seat insert and door card restorations.</t>
         </is>
       </c>
-      <c r="J14" s="1" t="n"/>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>クラシックポルシェ内装向けヴィンテージスタイルの縦ピンストライプベロア生地。高級シートインサートおよびドアカードレストアに最適。</t>
+        </is>
+      </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA3217.jpg</t>
@@ -1138,25 +1347,41 @@
           <t>PORSCHE STUDIO</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n"/>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ スタジオ</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>This is an authentic reproduction of Porsche’s iconic "Studio Check" automotive upholstery fabric, specifically curated for  Porsche 911 Carrera (964/993 generations), Porsche 928, and Porsche 968</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ911カレラ（964/993世代）、ポルシェ928、ポルシェ968向けにキュレーションされた、ポルシェの象徴的な「スタジオチェック」自動車用張り地の本格的な復刻版。</t>
+        </is>
+      </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
           <t>Porsche Studio Check Grey Fabric | 964 993 928 Restoration Cloth</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n"/>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ スタジオチェック グレー生地 | 964 993 928 レストアクロス</t>
+        </is>
+      </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
           <t>Vintage Authentic reproduction of the classic Porsche Studio Check upholstery fabric</t>
         </is>
       </c>
-      <c r="J15" s="1" t="n"/>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>クラシックポルシェスタジオチェック張り地のヴィンテージ本格復刻版。</t>
+        </is>
+      </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8118.jpg</t>
@@ -1183,25 +1408,41 @@
           <t>PORSCHE TARTAN</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n"/>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ タータン</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Introduced in 1975, this legendary pattern was famously optioned on the early Porsche 911 Turbo (930) and the 911SC</t>
         </is>
       </c>
-      <c r="F16" s="1" t="n"/>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>1975年に導入されたこの伝説的なパターンは、アーリーポルシェ911ターボ（930）と911SCに有名なオプションとして採用されました。</t>
+        </is>
+      </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
           <t>Porsche Classic Tartan Fabric | 911SC &amp; 930 Turbo Seat Cloth</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n"/>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>ポルシェ クラシック タータン生地 | 911SC &amp; 930ターボ シートクロス</t>
+        </is>
+      </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
           <t>Vintage-style  plaid upholstery cloth for classic Porsche interiors. Durable, period-correct flatwoven check fabric for seats and door cards.</t>
         </is>
       </c>
-      <c r="J16" s="1" t="n"/>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>クラシックポルシェ内装向けヴィンテージスタイルのプレイド張り地クロス。シートおよびドアカード用の耐久性のある時代考証フラットウーブンチェック生地。</t>
+        </is>
+      </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8217.jpg</t>
@@ -1228,25 +1469,41 @@
           <t>SELETED PLAID</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n"/>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>セレクテッド プレイド</t>
+        </is>
+      </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Selected plaid for automotive seat upholstery</t>
         </is>
       </c>
-      <c r="F17" s="1" t="n"/>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>自動車シート張り地向けセレクトプレイド。</t>
+        </is>
+      </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Automotive Plaid for Seat Upholstery </t>
         </is>
       </c>
-      <c r="H17" s="1" t="n"/>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>自動車用プレイド シート張り地</t>
+        </is>
+      </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Polyester automtive plaid for seat upholstery </t>
         </is>
       </c>
-      <c r="J17" s="1" t="n"/>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>自動車シート張り地向けポリエステルプレイド。</t>
+        </is>
+      </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA8517.jpg</t>
@@ -1273,25 +1530,41 @@
           <t>SPIRIT OF LE MANS</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n"/>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>スピリット・オブ・ル・マン</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>The Spirit of Le Mans (SOLM) Wool Line is a premium, motorsport-inspired tartan collection woven in Scotland and engineered specifically for high-end automotive interiors. 100% premium wool woven in a durable 2/2 twill, featuring a heavy-duty weight of 500 glm (365 gsm). Pre-treated with specialized Soil Resist and Fire Retardant (FR) compliance coatings tailored for automotive safety standards.</t>
         </is>
       </c>
-      <c r="F18" s="1" t="n"/>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Sprit of Le Mans（SOLM）ウールラインは、スコットランドで織られ、高級自動車内装専用に設計された、モータースポーツにインスパイアされたプレミアムタータンコレクション。100%プレミアムウール、耐久性のある2/2ツイル織り、ヘビーデューティーウェイト500 glm（365 gsm）。自動車安全基準に適合した専用の防汚・難燃（FR）コーティング済み。</t>
+        </is>
+      </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
           <t>100% Luxury Wool Automotive Fabric | Fire Retardant Tartan</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n"/>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>100%高級ウール 自動車用生地 | 難燃タータン</t>
+        </is>
+      </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
           <t>Heavyweight wool racing tartan cloth for luxury car interiors. Pre-treated with fire-retardant and soil-resist coatings. Woven in Scotland</t>
         </is>
       </c>
-      <c r="J18" s="1" t="n"/>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>高級車内装向けヘビーウェイトウールレーシングタータンクロス。難燃・防汚コーティング済み。スコットランド製。</t>
+        </is>
+      </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
           <t>/uploads/fabric/Cover/FA2002.jpg</t>
@@ -1302,73 +1575,234 @@
       <c r="N18" s="1" t="n"/>
       <c r="O18" s="1" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="n"/>
-      <c r="C19" s="1" t="n"/>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bmw-tartan</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>BMW TARTAN</t>
+        </is>
+      </c>
       <c r="D19" s="1" t="n"/>
-      <c r="E19" s="1" t="n"/>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>BMW ÜBERKARO is a classic tartan plaid fabric, famously known for its appearance in the legendary BMW E30 and the ultra-rare M3 Evolution II.</t>
+        </is>
+      </c>
       <c r="F19" s="1" t="n"/>
-      <c r="G19" s="1" t="n"/>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>Automotive Tartan Plaid Fabric, Upholstery for BMW E30 &amp; M3 Restoration</t>
+        </is>
+      </c>
       <c r="H19" s="1" t="n"/>
-      <c r="I19" s="1" t="n"/>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>Restore your classic BMW cabin with premium ÜBERKARO fabric. Woven to exact original specifications, this iconic E30 and M3 Evo II tartan plaid cloth matches the original factory pattern, color depth, and durability for a flawless showroom finish.</t>
+        </is>
+      </c>
       <c r="J19" s="1" t="n"/>
-      <c r="K19" s="1" t="n"/>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Cover/FA8275.jpeg</t>
+        </is>
+      </c>
       <c r="L19" s="1" t="n"/>
       <c r="M19" s="1" t="n"/>
       <c r="N19" s="1" t="n"/>
       <c r="O19" s="1" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1" t="n"/>
-      <c r="C20" s="1" t="n"/>
+    <row r="20" ht="118" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bmw-houndstooth</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>BMW HOUNDSTOOTH</t>
+        </is>
+      </c>
       <c r="D20" s="1" t="n"/>
-      <c r="E20" s="1" t="n"/>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Restore classic BMW interiors with our premium German-reproduction Houndstooth (Pepita) seat cloth. This high-durability wool-blend fabric provides an authentic texture and finish for vintage BMW E10 (2002), E21, E28 (5 Series), and E30 (3 Series, including the 325i and early M3 variants). It is the ideal choice for concours-level seat center inserts, door cards, and complete interior restorations.</t>
+        </is>
+      </c>
       <c r="F20" s="1" t="n"/>
-      <c r="G20" s="1" t="n"/>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>BMW Houndstooth Fabric | Classic E30, E28, 2002 Upholstery Cloth</t>
+        </is>
+      </c>
       <c r="H20" s="1" t="n"/>
-      <c r="I20" s="1" t="n"/>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>Premium OEM-spec BMW Houndstooth (Pepita) seat fabric by the meter. Period-correct wool blend for classic E30, E28, and 2002 interior restoration.</t>
+        </is>
+      </c>
       <c r="J20" s="1" t="n"/>
-      <c r="K20" s="1" t="n"/>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Cover/FA1817.jpg</t>
+        </is>
+      </c>
       <c r="L20" s="1" t="n"/>
       <c r="M20" s="1" t="n"/>
       <c r="N20" s="1" t="n"/>
       <c r="O20" s="1" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="1" t="n"/>
-      <c r="C21" s="1" t="n"/>
+    <row r="21" ht="137" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>mercedes-houndstooth</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>MERCEDES HOUNDSTOOTH</t>
+        </is>
+      </c>
       <c r="D21" s="1" t="n"/>
-      <c r="E21" s="1" t="n"/>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Restore the interior of your vintage W110 "Fintail" (Heckflosse) sedan with this premium reproduction houndstooth upholstery cloth. Woven to match the exact factory specifications of early 1960s mid-size Mercedes models, this dual-tone checkered fabric is a period-correct match for textile interiors in the 190c, 190Dc, and early 220 variants.</t>
+        </is>
+      </c>
       <c r="F21" s="1" t="n"/>
-      <c r="G21" s="1" t="n"/>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>Mercedes W110 Houndstooth Fabric | Vintage 190 &amp; 220 Seat Upholstery</t>
+        </is>
+      </c>
       <c r="H21" s="1" t="n"/>
-      <c r="I21" s="1" t="n"/>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz W110 Houndstooth seat cloth. Period-correct reproduction fabric for classic 190c, 190Dc, and 220 Fintail restoration by the meter.</t>
+        </is>
+      </c>
       <c r="J21" s="1" t="n"/>
-      <c r="K21" s="1" t="n"/>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Cover/FA8024.jpeg</t>
+        </is>
+      </c>
       <c r="L21" s="1" t="n"/>
       <c r="M21" s="1" t="n"/>
       <c r="N21" s="1" t="n"/>
       <c r="O21" s="1" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="1" t="n"/>
-      <c r="C22" s="1" t="n"/>
+    <row r="22" ht="168" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>VW TARTAN</t>
+        </is>
+      </c>
       <c r="D22" s="1" t="n"/>
-      <c r="E22" s="1" t="n"/>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>Premium-reproduction Volkswagen T2 Westfalia upholstery fabric. Meticulously woven to match the exact factory specifications of the 1968–1979 Type 2 Campmobile models, this iconic checkered plaid utilizes a heavy-duty, dense weave</t>
+        </is>
+      </c>
       <c r="F22" s="1" t="n"/>
-      <c r="G22" s="1" t="n"/>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>VW T2 Westfalia Fabric | Classic Camper Plaid Seat Upholstery</t>
+        </is>
+      </c>
       <c r="H22" s="1" t="n"/>
-      <c r="I22" s="1" t="n"/>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>VW T2 Westfalia plaid camper upholstery fabric. Premium reproduction cloth for classic Bay Window rock-and-roll beds.</t>
+        </is>
+      </c>
       <c r="J22" s="1" t="n"/>
-      <c r="K22" s="1" t="n"/>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Cover/FA8715.jpeg</t>
+        </is>
+      </c>
       <c r="L22" s="1" t="n"/>
       <c r="M22" s="1" t="n"/>
       <c r="N22" s="1" t="n"/>
       <c r="O22" s="1" t="n"/>
+    </row>
+    <row r="23" ht="75" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ferrari-technical</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>FERRARI TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>フェラーリ テクニカル</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Original Ferrari technical fabric used in 488 Pista, 812 Superfast etc. This synthetic textile prioritizes uncompromised motorsport performance over traditional luxury leather</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>Original Ferrari 488 Pista Technical Fabric | OEM Racing Seat Material</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>Source genuine Ferrari 488 Pista technical racing fabric. Perfect OEM-spec material for high-grip seat inserts, lightweight floor mats, and track upholstery.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Cover/FA1269.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Ferrari Technical/FA1269.jpeg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1381,7 +1815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="34.1640625" customWidth="1" min="1" max="1"/>
@@ -4407,6 +4841,881 @@
       <c r="H86" t="inlineStr">
         <is>
           <t>イギリス</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>bmw-tartan</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>bmw-tartan</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>bmw-tartan</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>bmw-tartan</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>bmw-tartan</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>bmw-houndstooth</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1.1mm</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1.1mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>bmw-houndstooth</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>bmw-houndstooth</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>bmw-houndstooth</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>4</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Wool/Polyester</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ウール/ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>bmw-houndstooth</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>5</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>mercedes-houndstooth</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1.0mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>mercedes-houndstooth</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>mercedes-houndstooth</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>3</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>mercedes-houndstooth</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Wool</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ウール</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>mercedes-houndstooth</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.9mm</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0.9mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Polyester</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>5</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>ferrari-technical</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>厚さ</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0.85mm</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>0.9mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>ferrari-technical</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>自動車用</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>ferrari-technical</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>width</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>WIDTH</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>幅</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>140cm</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>140CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>ferrari-technical</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>4</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>素材</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Polyester</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ポリエステル</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>ferrari-technical</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>5</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>country of origin</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>COUNTRY OF ORIGIN</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>製造国</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
         </is>
       </c>
     </row>
@@ -4503,12 +5812,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="20.1640625" customWidth="1" min="3" max="3"/>
     <col width="36.83203125" customWidth="1" min="5" max="5"/>
     <col width="21.33203125" customWidth="1" min="6" max="6"/>
+    <col width="65.83203125" customWidth="1" min="8" max="8"/>
+    <col width="58.5" customWidth="1" min="9" max="9"/>
     <col width="35.83203125" customWidth="1" min="10" max="10"/>
     <col width="25" customWidth="1" min="11" max="11"/>
     <col width="30.1640625" customWidth="1" min="12" max="13"/>
@@ -6249,7 +7560,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="240" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
           <t>fa8517</t>
@@ -6290,13 +7601,28 @@
           <t>/uploads/fabric/Preview/FA8517.jpg</t>
         </is>
       </c>
+      <c r="K37" s="1" t="inlineStr">
+        <is>
+          <t>Bespoke automotive seats with this premium foamed fabric. It is inspired directly by the historic legacy of the Porsche Sonderwunsch . Showcased as the defining pattern of the 992-generation 911 Turbo Sonderwunsch edition, this textile reimagines the iconic 1974 "Louise" Turbo No. 1 heritage cabin layout with a striking red, blue, and black checkered weave.</t>
+        </is>
+      </c>
+      <c r="M37" s="1" t="inlineStr">
+        <is>
+          <t>Porsche Sonderwunsch Fabric | Red Blue Black Plaid Upholstery</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>Premium OEM-spec Porsche Sonderwunsch program red, blue, and black plaid fabric. Foam-backed heritage seat cloth for custom 911 interior</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>/uploads/fabric/Selected Plaid/FA8517.jpg</t>
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="120" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
           <t>fa8553</t>
@@ -6337,16 +7663,31 @@
           <t>/uploads/fabric/Preview/FA8553.jpg</t>
         </is>
       </c>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>Premium reproduction "Carla" check upholstery fabric, famously featured in the late 1970s and 1980s Ford Capri S models (Mk2 and Mk3)</t>
+        </is>
+      </c>
+      <c r="M38" s="1" t="inlineStr">
+        <is>
+          <t>Ford Capri S Carla Fabric | Classic Orange &amp; Grey Plaid Upholstery</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>Ford Capri S "Carla" check seat fabric. Premium orange, grey, and black reproduction cloth for classic Mk2 &amp; Mk3 Capri interior restoration</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>/uploads/fabric/Selected Plaid/FA8553.jpg</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="210" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fa2002</t>
+          <t>fa8075</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6356,44 +7697,59 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>spirit-of-le-mans</t>
+          <t>selected-plaid</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FA2002</t>
+          <t>FA8075</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BLUE/NAVY/RED</t>
+          <t>GRAY/BLUE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+          <t>/uploads/fabric/Selected Plaid/FA8075.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+          <t>/uploads/fabric/Selected Plaid/FA8075.jpg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Preview/FA2002.jpg</t>
+          <t>/uploads/fabric/Preview/FA8075.jpeg</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr">
+        <is>
+          <t>Restore the authentic interior of late-production Mexican-built Volkswagen Beetles—variously known as the Käfer, Kever, or Coccinelle—with our premium reproduction upholstery fabric which replicates the exact factory texture of the late 1970s through the 1980s Puebla production era</t>
+        </is>
+      </c>
+      <c r="M39" s="1" t="inlineStr">
+        <is>
+          <t>VW Beetle Mexico Heavy-duty Fabric | Classic Käfer &amp; Coccinelle Upholstery</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>VW Beetle Mexico (Käfer/Kever) striped heavy-duty seat fabric . Premium reproduction cloth for classic Puebla-built interiors.</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
+          <t>/uploads/fabric/Selected Plaid/FA8075.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="105" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fa2202</t>
+          <t>fa8072</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6403,84 +7759,817 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>spirit-of-le-mans</t>
+          <t>selected-plaid</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FA2202</t>
+          <t>FA8072</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BLUE/ORANGE/NAVY</t>
+          <t>BLACK/WHITE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+          <t>/uploads/fabric/Selected Plaid/FA8072.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+          <t>/uploads/fabric/Selected Plaid/FA8072.jpg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Preview/FA2202.jpg</t>
+          <t>/uploads/fabric/Preview/FA8072.jpeg</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>upgrade your modern classic with our premium Satellite Grey upholstery material, engineered specifically for the third-generation MINI Cooper  (F56)</t>
+        </is>
+      </c>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t>MINI F56 Satellite Grey Fabric | MINI Cooper Seat Upholstery Material</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>Premium OEM-spec MINI F56 Satellite Grey cloth. Perfect for third-gen Cooper &amp; Cooper S seat and door panel restorations.</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+          <t>/uploads/fabric/Selected Plaid/FA8072.jpg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>fa2002</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>FA2002</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BLUE/NAVY/RED</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA2002.jpg</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2002.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fa2202</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>spirit-of-le-mans</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FA2202</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BLUE/ORANGE/NAVY</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA2202.jpg</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Spirit of Le Mans/FA2202.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>fa2729</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>fabric</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>spirit-of-le-mans</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>FA2729</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>BLUE/BLACK/RED</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>/uploads/fabric/Preview/FA2729.jpg</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>/uploads/fabric/Spirit of Le Mans/FA2729.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fa1817</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>bmw-houndstooth</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FA1817</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DARK GRAY</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Houndstooth/FA1817.jpg</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Houndstooth/FA1817.jpg</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA1817.jpg</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Houndstooth/FA1817.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fa1815</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>bmw-houndstooth</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FA1815</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LIGHT GRAY</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Houndstooth/FA1815.jpg</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Houndstooth/FA1815.jpg</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA1815.jpg</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Houndstooth/FA1815.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fa8275</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>bmw-tartan</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>FA8275</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BROWN/WHITE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Tartan/FA8275.jpg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Tartan/FA8275.jpg</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8275.jpeg</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Tartan/FA8275.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fa9368</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>bmw-tartan</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>FA9368</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Tartan/FA9368.jpg</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Tartan/FA9368.jpg</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA9368.jpeg</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/BMW Tartan/FA9368.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fa8024</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>mercedes-houndstooth</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>FA8024</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BLUE/WHITE</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Houndstooth/FA8024.jpg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Houndstooth/FA8024.jpg</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8024.jpeg</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Houndstooth/FA8024.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fa8066</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>mercedes-houndstooth</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FA8066</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BLACK/BEIGE</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Houndstooth/FA8066.jpg</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Houndstooth/FA8066.jpg</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8066.jpeg</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Mercedes Houndstooth/FA8066.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fa8715</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FA8715</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ORAGNE/YELLOW</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8715.jpg</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8715.jpg</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8715.jpeg</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8715.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fa8726</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>FA8726</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BLUE/GREEN</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8726.jpg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8726.jpg</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8726.jpeg</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8726.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fa8734</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FA8734</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GREEN/YELLOW</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8734.jpg</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8734.jpg</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8734.jpeg</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8734.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fa8754</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>vw-tartan</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FA8754</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BROWN/BEIGE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8754.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8754.jpg</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA8754.jpeg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/VW Tartan/FA8754.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ferrari-technical-fa1228</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ferrari-technical</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>FA1228</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>FA1228</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FA1228</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>#111111</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Ferrari Technical/FA1228.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Ferrari Technical/FA1228.jpg</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA1228.jpeg</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Ferrari technical fabric for performance-oriented automotive interiors.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>パフォーマンス志向の自動車内装向けフェラーリ テクニカルファブリック。</t>
+        </is>
+      </c>
+      <c r="M54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ferrari Technical Blue Fabric FR | 488 Pista Racing Seat Insert and Floor Mat</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>Orignal Ferrari technical black fabric for racing seat inserts and automotive upholstery.</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Ferrari Technical/FA1228.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="75" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ferrari-technical-fa1269</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ferrari-technical</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>FA1269</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>FA1269</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>FA1269</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>#1d1d1d</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Ferrari Technical/FA1269.jpg</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Ferrari Technical/FA1269.jpg</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Preview/FA1269.jpeg</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ferrari technical fabric for performance-oriented automotive interiors.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>パフォーマンス志向の自動車内装向けフェラーリ テクニカルファブリック。</t>
+        </is>
+      </c>
+      <c r="M55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ferrari Technical Black Fabric FR | 488 Pista Racing Seat Insert and Floor Mat</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>Orignal Ferrari technical fabric for racing seat inserts and automotive upholstery.</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Ferrari Technical/FA1269.jpg</t>
         </is>
       </c>
     </row>
@@ -6597,8 +8686,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="14.6640625" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -7224,6 +9316,471 @@
       <c r="C41" t="inlineStr">
         <is>
           <t>/uploads/fabric/Case/FA2729.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fa2002</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA2002.JPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fa2202</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA2202.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fa2729</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA2729-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fa2729</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA2729-3.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fa2729</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA2729.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>fa3018</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA3018.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fa3132</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA3132.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>fa5990</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/ FA5990.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>fa8045</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8045.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>fa8063</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8063.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fa8065</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8065.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fa8074</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8074-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fa8074</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8074.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fa8093</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8093.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fa8118</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8118.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fa8165</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/ FA8165-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fa8165</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/ FA8165.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fa8271</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8271-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fa8271</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8271-3.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fa8271</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8271.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fa8354</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8354-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fa8354</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8354.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fa8475</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8475.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>fa8517</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8517.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>fa8525</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8525.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fa8626</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8626-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fa8626</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA8626.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ferrari-technical-fa1269</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA1269.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ferrari-technical-fa1228</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA1228.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ferrari-technical-fa1269</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA1269-2.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ferrari-technical-fa1269</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>/uploads/fabric/Casephoto/FA1269-3.jpeg</t>
         </is>
       </c>
     </row>
